--- a/sources/king_step5.xlsx
+++ b/sources/king_step5.xlsx
@@ -1113,6 +1113,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>67ff2023-6e37-4766-ab77-10e230c708b4</t>
+        </is>
+      </c>
       <c r="Q14" t="inlineStr">
         <is>
           <t>67ff2023-6e37-4766-ab77-10e230c708b4</t>
@@ -1155,6 +1160,11 @@
           <t>3+4</t>
         </is>
       </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>c4c3cd71-ed27-44df-a655-fb09f78b6be8</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>c4c3cd71-ed27-44df-a655-fb09f78b6be8</t>
@@ -1197,6 +1207,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>f8794d93-a444-4657-859f-d2548700e248</t>
+        </is>
+      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>f8794d93-a444-4657-859f-d2548700e248</t>
@@ -1239,6 +1254,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>9821af5c-9a74-43da-8d33-7092f2b7ff7b</t>
+        </is>
+      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>9821af5c-9a74-43da-8d33-7092f2b7ff7b</t>
@@ -1291,6 +1311,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>7df0cfa5-026b-4ff9-9f39-55c477962d0f</t>
+        </is>
+      </c>
       <c r="Q18" t="inlineStr">
         <is>
           <t>7df0cfa5-026b-4ff9-9f39-55c477962d0f</t>
@@ -1328,6 +1353,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>f8490fa0-7b1f-4f39-99ab-da6ae361ed20</t>
+        </is>
+      </c>
       <c r="Q19" t="inlineStr">
         <is>
           <t>f8490fa0-7b1f-4f39-99ab-da6ae361ed20</t>
@@ -1370,6 +1400,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>68f074ca-3602-4223-bca2-a6b2ec87ef2a</t>
+        </is>
+      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>68f074ca-3602-4223-bca2-a6b2ec87ef2a</t>
@@ -1412,6 +1447,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>0176585b-588a-49e1-9572-4bdd7101f82a</t>
+        </is>
+      </c>
       <c r="Q21" t="inlineStr">
         <is>
           <t>0176585b-588a-49e1-9572-4bdd7101f82a</t>
@@ -1454,6 +1494,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>00ddf7e7-6010-4a77-9ae6-40ef2f2a707a</t>
+        </is>
+      </c>
       <c r="Q22" t="inlineStr">
         <is>
           <t>00ddf7e7-6010-4a77-9ae6-40ef2f2a707a</t>
@@ -1496,6 +1541,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>b6c23f31-cb1a-450f-9a17-e7cc5b124033</t>
+        </is>
+      </c>
       <c r="Q23" t="inlineStr">
         <is>
           <t>b6c23f31-cb1a-450f-9a17-e7cc5b124033</t>
@@ -1538,6 +1588,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>12308a0d-a04e-49ad-a92e-7b32fb03c49f</t>
+        </is>
+      </c>
       <c r="Q24" t="inlineStr">
         <is>
           <t>12308a0d-a04e-49ad-a92e-7b32fb03c49f</t>
@@ -1580,6 +1635,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>6c0cc2bf-f0ad-4b46-a1ff-2a7de8bdb37f</t>
+        </is>
+      </c>
       <c r="Q25" t="inlineStr">
         <is>
           <t>6c0cc2bf-f0ad-4b46-a1ff-2a7de8bdb37f</t>
@@ -1622,6 +1682,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>377bd68e-1783-43e2-8c72-05143260300a</t>
+        </is>
+      </c>
       <c r="Q26" t="inlineStr">
         <is>
           <t>377bd68e-1783-43e2-8c72-05143260300a</t>
@@ -1664,6 +1729,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>f57394c8-7aba-414b-af3e-d37941cae2e3</t>
+        </is>
+      </c>
       <c r="Q27" t="inlineStr">
         <is>
           <t>f57394c8-7aba-414b-af3e-d37941cae2e3</t>
@@ -1716,6 +1786,11 @@
           <t>The Counter Hit Stomach Smash is NOT a throw but is required before you can do the 2 throw follow ups.</t>
         </is>
       </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>b2d4546c-7d86-4fee-a8f7-dbe4e5857d92</t>
+        </is>
+      </c>
       <c r="Q28" t="inlineStr">
         <is>
           <t>b2d4546c-7d86-4fee-a8f7-dbe4e5857d92</t>
@@ -1753,6 +1828,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>829ce921-0e10-4ab2-bbbc-911f844eceef</t>
+        </is>
+      </c>
       <c r="Q29" t="inlineStr">
         <is>
           <t>829ce921-0e10-4ab2-bbbc-911f844eceef</t>
@@ -1795,6 +1875,11 @@
           <t>3+4</t>
         </is>
       </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>db0aa370-9079-45e2-b39c-7472d8bae8a4</t>
+        </is>
+      </c>
       <c r="Q30" t="inlineStr">
         <is>
           <t>db0aa370-9079-45e2-b39c-7472d8bae8a4</t>
@@ -1847,6 +1932,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>6294b53d-e480-4df4-be9f-98a25b5e6a95</t>
+        </is>
+      </c>
       <c r="Q31" t="inlineStr">
         <is>
           <t>6294b53d-e480-4df4-be9f-98a25b5e6a95</t>
@@ -1894,6 +1984,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>16314dd7-17de-43e3-89e8-146678a228d1</t>
+        </is>
+      </c>
       <c r="Q32" t="inlineStr">
         <is>
           <t>16314dd7-17de-43e3-89e8-146678a228d1</t>
@@ -1941,6 +2036,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>ab65c71e-57c4-4826-b7e0-038c4501bdc6</t>
+        </is>
+      </c>
       <c r="Q33" t="inlineStr">
         <is>
           <t>ab65c71e-57c4-4826-b7e0-038c4501bdc6</t>
@@ -1983,6 +2083,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>fe0b77cb-f2dd-4ba4-b684-d4ecf9d4a053</t>
+        </is>
+      </c>
       <c r="Q34" t="inlineStr">
         <is>
           <t>fe0b77cb-f2dd-4ba4-b684-d4ecf9d4a053</t>
@@ -2023,6 +2128,11 @@
       <c r="M35" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>a7a77dd9-2c48-4420-8555-24aab9d0520c</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -2177,6 +2287,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>014ddb56-1613-49f0-9e34-a5e1f6c785fe</t>
+        </is>
+      </c>
       <c r="Q39" t="inlineStr">
         <is>
           <t>014ddb56-1613-49f0-9e34-a5e1f6c785fe</t>
@@ -2224,6 +2339,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>8b30b6c0-0bc1-4441-8820-964886587202</t>
+        </is>
+      </c>
       <c r="Q40" t="inlineStr">
         <is>
           <t>8b30b6c0-0bc1-4441-8820-964886587202</t>
@@ -2266,6 +2386,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>1a628a44-4c66-4d94-b410-673005311f11</t>
+        </is>
+      </c>
       <c r="Q41" t="inlineStr">
         <is>
           <t>1a628a44-4c66-4d94-b410-673005311f11</t>
@@ -2308,6 +2433,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>912252eb-66d4-4874-abc8-0c9951b57b07</t>
+        </is>
+      </c>
       <c r="Q42" t="inlineStr">
         <is>
           <t>912252eb-66d4-4874-abc8-0c9951b57b07</t>
@@ -2350,6 +2480,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>78755529-5600-440c-8380-ad656059ff13</t>
+        </is>
+      </c>
       <c r="Q43" t="inlineStr">
         <is>
           <t>78755529-5600-440c-8380-ad656059ff13</t>
@@ -2397,6 +2532,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>3d784cd2-6e86-46a8-bbd0-6f0b4d5c473c</t>
+        </is>
+      </c>
       <c r="Q44" t="inlineStr">
         <is>
           <t>3d784cd2-6e86-46a8-bbd0-6f0b4d5c473c</t>
@@ -2444,6 +2584,11 @@
           <t>3+4</t>
         </is>
       </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>97fdc64c-6825-4fbc-b64c-406c522a9288</t>
+        </is>
+      </c>
       <c r="Q45" t="inlineStr">
         <is>
           <t>97fdc64c-6825-4fbc-b64c-406c522a9288</t>
@@ -2491,6 +2636,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>4b9555c8-11ce-4fb0-af28-67c8956588ae</t>
+        </is>
+      </c>
       <c r="Q46" t="inlineStr">
         <is>
           <t>4b9555c8-11ce-4fb0-af28-67c8956588ae</t>
@@ -2538,6 +2688,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>cb6d3d00-45b4-40eb-8e80-dff09bade591</t>
+        </is>
+      </c>
       <c r="Q47" t="inlineStr">
         <is>
           <t>cb6d3d00-45b4-40eb-8e80-dff09bade591</t>
@@ -2583,6 +2738,11 @@
       <c r="M48" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>44cede5f-e666-42c2-b9ea-20ca0d73478e</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -6999,6 +7159,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>d14fb2bb-b9cb-4ac9-9db3-e052c90daa2f</t>
+        </is>
+      </c>
       <c r="Q132" t="inlineStr">
         <is>
           <t>d14fb2bb-b9cb-4ac9-9db3-e052c90daa2f</t>
@@ -7036,6 +7201,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>754287bc-eb16-4fb1-adf5-9ba198ef61bc</t>
+        </is>
+      </c>
       <c r="Q133" t="inlineStr">
         <is>
           <t>754287bc-eb16-4fb1-adf5-9ba198ef61bc</t>
@@ -7078,6 +7248,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>610d1988-6af6-4bcc-a947-eb4020bc3119</t>
+        </is>
+      </c>
       <c r="Q134" t="inlineStr">
         <is>
           <t>610d1988-6af6-4bcc-a947-eb4020bc3119</t>
@@ -7120,6 +7295,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>ffa2eb74-b7c8-48f6-b268-2882ba61fae0</t>
+        </is>
+      </c>
       <c r="Q135" t="inlineStr">
         <is>
           <t>ffa2eb74-b7c8-48f6-b268-2882ba61fae0</t>
@@ -7162,6 +7342,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>318177e8-8c06-4cfe-a628-4c3f588e36e9</t>
+        </is>
+      </c>
       <c r="Q136" t="inlineStr">
         <is>
           <t>318177e8-8c06-4cfe-a628-4c3f588e36e9</t>
@@ -7214,6 +7399,11 @@
           <t>After the initial grab use 3+4 to escape.</t>
         </is>
       </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>e9174a35-b2b1-40d7-8704-552434c99980</t>
+        </is>
+      </c>
       <c r="Q137" t="inlineStr">
         <is>
           <t>e9174a35-b2b1-40d7-8704-552434c99980</t>
@@ -7256,6 +7446,11 @@
           <t>Double Arm Face Buster is not additional damage to the Jaguar Driver, it add 5 points of damage.</t>
         </is>
       </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>61fbd176-0a6e-4368-89b2-fae51c957338</t>
+        </is>
+      </c>
       <c r="Q138" t="inlineStr">
         <is>
           <t>61fbd176-0a6e-4368-89b2-fae51c957338</t>
@@ -7298,6 +7493,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>e370e475-82e9-42c2-9dda-e815185d01ba</t>
+        </is>
+      </c>
       <c r="Q139" t="inlineStr">
         <is>
           <t>e370e475-82e9-42c2-9dda-e815185d01ba</t>
@@ -7345,6 +7545,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>d0dc416c-d281-41de-a830-391175b9c733</t>
+        </is>
+      </c>
       <c r="Q140" t="inlineStr">
         <is>
           <t>d0dc416c-d281-41de-a830-391175b9c733</t>
@@ -7382,6 +7587,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>c1efc095-a281-425f-89ef-e6a21a09748e</t>
+        </is>
+      </c>
       <c r="Q141" t="inlineStr">
         <is>
           <t>c1efc095-a281-425f-89ef-e6a21a09748e</t>
@@ -7424,6 +7634,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>ca3bdbfd-726c-4c6a-8a68-16d368d953de</t>
+        </is>
+      </c>
       <c r="Q142" t="inlineStr">
         <is>
           <t>ca3bdbfd-726c-4c6a-8a68-16d368d953de</t>
@@ -7466,6 +7681,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>576fbd03-9817-4433-aee9-a05fb2873ee9</t>
+        </is>
+      </c>
       <c r="Q143" t="inlineStr">
         <is>
           <t>576fbd03-9817-4433-aee9-a05fb2873ee9</t>
@@ -7508,6 +7728,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>bf90b650-01f4-4fc9-88b8-319864f95c86</t>
+        </is>
+      </c>
       <c r="Q144" t="inlineStr">
         <is>
           <t>bf90b650-01f4-4fc9-88b8-319864f95c86</t>
@@ -7550,6 +7775,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>9cb56a53-599f-4719-9b84-f7e40bb6afa8</t>
+        </is>
+      </c>
       <c r="Q145" t="inlineStr">
         <is>
           <t>9cb56a53-599f-4719-9b84-f7e40bb6afa8</t>
@@ -7592,6 +7822,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>c053f961-d2f8-4fbd-83ae-34fca200b9b7</t>
+        </is>
+      </c>
       <c r="Q146" t="inlineStr">
         <is>
           <t>c053f961-d2f8-4fbd-83ae-34fca200b9b7</t>
@@ -7649,6 +7884,11 @@
           <t>Escape with 1 if the multi was started with 1+3 and 2 if the multi was started with 2+4.</t>
         </is>
       </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>8a657c3c-5962-4744-8afb-8db34e185b60</t>
+        </is>
+      </c>
       <c r="Q147" t="inlineStr">
         <is>
           <t>8a657c3c-5962-4744-8afb-8db34e185b60</t>
@@ -7691,6 +7931,11 @@
           <t>Escape with 1 if the multi was started with 1+3 and 2 if the multi was started with 2+4.</t>
         </is>
       </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>e9b59331-5359-43c8-a2fe-c2f1c768010e</t>
+        </is>
+      </c>
       <c r="Q148" t="inlineStr">
         <is>
           <t>e9b59331-5359-43c8-a2fe-c2f1c768010e</t>
@@ -7733,6 +7978,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>a35b6adb-c2ae-4dcc-8c1c-e89ddf41df28</t>
+        </is>
+      </c>
       <c r="Q149" t="inlineStr">
         <is>
           <t>a35b6adb-c2ae-4dcc-8c1c-e89ddf41df28</t>
@@ -7775,6 +8025,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>a076bd88-cfd9-4b82-b29b-751f8994df70</t>
+        </is>
+      </c>
       <c r="Q150" t="inlineStr">
         <is>
           <t>a076bd88-cfd9-4b82-b29b-751f8994df70</t>
@@ -7817,6 +8072,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>897562ea-11c8-48e1-bdd7-3508028d9455</t>
+        </is>
+      </c>
       <c r="Q151" t="inlineStr">
         <is>
           <t>897562ea-11c8-48e1-bdd7-3508028d9455</t>
@@ -7859,6 +8119,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>0499e709-28d1-44ad-884c-143bf75b7436</t>
+        </is>
+      </c>
       <c r="Q152" t="inlineStr">
         <is>
           <t>0499e709-28d1-44ad-884c-143bf75b7436</t>
@@ -7901,6 +8166,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>988107cd-c43e-41b1-bec3-f6450eebd275</t>
+        </is>
+      </c>
       <c r="Q153" t="inlineStr">
         <is>
           <t>988107cd-c43e-41b1-bec3-f6450eebd275</t>
@@ -7943,6 +8213,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>54aa2be5-501e-441f-b759-e6eaa8b2c7aa</t>
+        </is>
+      </c>
       <c r="Q154" t="inlineStr">
         <is>
           <t>54aa2be5-501e-441f-b759-e6eaa8b2c7aa</t>
@@ -7985,6 +8260,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>e36e2276-3cc6-43b4-bef5-0d88f962c067</t>
+        </is>
+      </c>
       <c r="Q155" t="inlineStr">
         <is>
           <t>e36e2276-3cc6-43b4-bef5-0d88f962c067</t>
@@ -8027,6 +8307,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>91806b57-15f2-453a-9e66-6e9265eb3f74</t>
+        </is>
+      </c>
       <c r="Q156" t="inlineStr">
         <is>
           <t>91806b57-15f2-453a-9e66-6e9265eb3f74</t>
@@ -8069,6 +8354,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>0d22dd12-3fab-495f-bd30-0dd66be69ec9</t>
+        </is>
+      </c>
       <c r="Q157" t="inlineStr">
         <is>
           <t>0d22dd12-3fab-495f-bd30-0dd66be69ec9</t>
@@ -8111,6 +8401,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>0b34d2a0-d07c-4603-9984-9e48ffa8b289</t>
+        </is>
+      </c>
       <c r="Q158" t="inlineStr">
         <is>
           <t>0b34d2a0-d07c-4603-9984-9e48ffa8b289</t>
@@ -8153,6 +8448,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>3a88bc91-07bf-4196-bbfc-65d00fdc5cdb</t>
+        </is>
+      </c>
       <c r="Q159" t="inlineStr">
         <is>
           <t>3a88bc91-07bf-4196-bbfc-65d00fdc5cdb</t>
@@ -8195,6 +8495,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>88d1f06b-09b4-4f3b-b26f-6b7eb09839b9</t>
+        </is>
+      </c>
       <c r="Q160" t="inlineStr">
         <is>
           <t>88d1f06b-09b4-4f3b-b26f-6b7eb09839b9</t>
@@ -8242,6 +8547,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>21a93725-b013-4fd7-b6a0-53b29c951345</t>
+        </is>
+      </c>
       <c r="Q161" t="inlineStr">
         <is>
           <t>21a93725-b013-4fd7-b6a0-53b29c951345</t>
@@ -8289,6 +8599,11 @@
           <t>If grabbed from the side or back then Cannonball will be the 1st part of the Multi Throw.</t>
         </is>
       </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>e5cfb3e7-d8eb-43a9-95a5-78b47376b89c</t>
+        </is>
+      </c>
       <c r="Q162" t="inlineStr">
         <is>
           <t>e5cfb3e7-d8eb-43a9-95a5-78b47376b89c</t>
@@ -8331,6 +8646,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>d29031f4-9c39-4518-8ca7-d1d579f731d3</t>
+        </is>
+      </c>
       <c r="Q163" t="inlineStr">
         <is>
           <t>d29031f4-9c39-4518-8ca7-d1d579f731d3</t>
@@ -8368,6 +8688,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>cf747642-f5e0-4884-9c87-bf258ea86c4c</t>
+        </is>
+      </c>
       <c r="Q164" t="inlineStr">
         <is>
           <t>cf747642-f5e0-4884-9c87-bf258ea86c4c</t>
@@ -8410,6 +8735,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>90ec3fb9-f4d7-421a-99e2-e37e4a49ce00</t>
+        </is>
+      </c>
       <c r="Q165" t="inlineStr">
         <is>
           <t>90ec3fb9-f4d7-421a-99e2-e37e4a49ce00</t>
@@ -8452,6 +8782,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>334b113e-5fa6-4350-8c7f-d1443e15e6b7</t>
+        </is>
+      </c>
       <c r="Q166" t="inlineStr">
         <is>
           <t>334b113e-5fa6-4350-8c7f-d1443e15e6b7</t>
@@ -8494,6 +8829,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>58f13036-58ee-4611-a14d-d783777422a0</t>
+        </is>
+      </c>
       <c r="Q167" t="inlineStr">
         <is>
           <t>58f13036-58ee-4611-a14d-d783777422a0</t>
@@ -8536,6 +8876,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>f7973f34-41fe-4bf5-95c3-8fb79ee2452d</t>
+        </is>
+      </c>
       <c r="Q168" t="inlineStr">
         <is>
           <t>f7973f34-41fe-4bf5-95c3-8fb79ee2452d</t>
@@ -8578,6 +8923,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>0515905e-bcfb-496f-bbfc-01dedb07caa4</t>
+        </is>
+      </c>
       <c r="Q169" t="inlineStr">
         <is>
           <t>0515905e-bcfb-496f-bbfc-01dedb07caa4</t>
@@ -8620,6 +8970,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>fefe8385-3ffe-4743-8071-1a48c86080c5</t>
+        </is>
+      </c>
       <c r="Q170" t="inlineStr">
         <is>
           <t>fefe8385-3ffe-4743-8071-1a48c86080c5</t>
@@ -8660,6 +9015,11 @@
       <c r="M171" t="inlineStr">
         <is>
           <t>2</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>cd229188-1f00-4e2c-beb7-0ecdab35b8dc</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
@@ -8804,6 +9164,11 @@
           <t>hhmmhLLLmM</t>
         </is>
       </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>540396d1-00a1-4033-9fce-7dbbcf91bebf</t>
+        </is>
+      </c>
       <c r="Q175" t="inlineStr">
         <is>
           <t>540396d1-00a1-4033-9fce-7dbbcf91bebf</t>
@@ -8836,6 +9201,11 @@
           <t>hhmmhLLLmh</t>
         </is>
       </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>53b541e0-d1fa-4602-8e8e-198dc6d57441</t>
+        </is>
+      </c>
       <c r="Q176" t="inlineStr">
         <is>
           <t>53b541e0-d1fa-4602-8e8e-198dc6d57441</t>
@@ -8868,6 +9238,11 @@
           <t>hhmmhmLLmM</t>
         </is>
       </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>d76e55af-5e37-469f-b459-858d5c452608</t>
+        </is>
+      </c>
       <c r="Q177" t="inlineStr">
         <is>
           <t>d76e55af-5e37-469f-b459-858d5c452608</t>
@@ -8900,6 +9275,11 @@
           <t>hhmmhmLLmh</t>
         </is>
       </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>10ceada9-d82e-41bd-b56c-5a3fa1400921</t>
+        </is>
+      </c>
       <c r="Q178" t="inlineStr">
         <is>
           <t>10ceada9-d82e-41bd-b56c-5a3fa1400921</t>
@@ -8932,6 +9312,11 @@
           <t>hhmmhmLLlthrow</t>
         </is>
       </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>5c5c8a42-acd0-4b4b-88f6-39a67110202e</t>
+        </is>
+      </c>
       <c r="Q179" t="inlineStr">
         <is>
           <t>5c5c8a42-acd0-4b4b-88f6-39a67110202e</t>
@@ -8964,6 +9349,11 @@
           <t>hmmhLLLmM</t>
         </is>
       </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>47c1d8e6-c95b-4542-b264-13a374b2c050</t>
+        </is>
+      </c>
       <c r="Q180" t="inlineStr">
         <is>
           <t>47c1d8e6-c95b-4542-b264-13a374b2c050</t>
@@ -8996,6 +9386,11 @@
           <t>hmmhLLLmh</t>
         </is>
       </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>76d4a800-1555-4b0e-a6b7-bdcb47516018</t>
+        </is>
+      </c>
       <c r="Q181" t="inlineStr">
         <is>
           <t>76d4a800-1555-4b0e-a6b7-bdcb47516018</t>
@@ -9028,6 +9423,11 @@
           <t>hmmhmLLmM</t>
         </is>
       </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>d3e32834-6f80-4957-ac5b-a1be0e260a44</t>
+        </is>
+      </c>
       <c r="Q182" t="inlineStr">
         <is>
           <t>d3e32834-6f80-4957-ac5b-a1be0e260a44</t>
@@ -9060,6 +9460,11 @@
           <t>hmmhmLLmh</t>
         </is>
       </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>3de5ed24-6134-418b-ba3e-f25a1039677a</t>
+        </is>
+      </c>
       <c r="Q183" t="inlineStr">
         <is>
           <t>3de5ed24-6134-418b-ba3e-f25a1039677a</t>
@@ -9090,6 +9495,11 @@
       <c r="K184" t="inlineStr">
         <is>
           <t>hmmhmLLlthrow</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>9aa5afc6-6646-4750-b84c-b3114de16321</t>
         </is>
       </c>
       <c r="Q184" t="inlineStr">

--- a/sources/king_step5.xlsx
+++ b/sources/king_step5.xlsx
@@ -1333,6 +1333,11 @@
           <t>– 1,2,1,2,1</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1,2,1,1,2</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
           <t>– Ultimate Punches</t>
@@ -1380,6 +1385,11 @@
           <t>– 2,1,2,1,2</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2,1,2,2,1</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
           <t>– Ultimate Punches</t>
@@ -1425,6 +1435,11 @@
       <c r="A21" t="inlineStr">
         <is>
           <t>– 1,2,1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2,1,2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
